--- a/artfynd/A 32779-2025 artfynd.xlsx
+++ b/artfynd/A 32779-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80557217</v>
+        <v>80557774</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Sverige, Ås lm</t>
+          <t>Norra sverige, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586240.8657898126</v>
+        <v>586339</v>
       </c>
       <c r="R2" t="n">
-        <v>7203765.854181414</v>
+        <v>7203636</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80557774</v>
+        <v>80556987</v>
       </c>
       <c r="B3" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra sverige, Ås lm</t>
+          <t>Norra Sverige, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586338.8989356026</v>
+        <v>586322</v>
       </c>
       <c r="R3" t="n">
-        <v>7203635.920533834</v>
+        <v>7203737</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80556987</v>
+        <v>80557217</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586321.9685981375</v>
+        <v>586241</v>
       </c>
       <c r="R4" t="n">
-        <v>7203736.808687928</v>
+        <v>7203766</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
